--- a/research/yjs-manual-opt/swiss/products/v23/i18n/workbooks/en.xlsx
+++ b/research/yjs-manual-opt/swiss/products/v23/i18n/workbooks/en.xlsx
@@ -4625,7 +4625,7 @@
         <v>**真空密封后袋子漏气**</v>
       </c>
       <c r="E184" t="str">
-        <v>**真空密封后袋子漏气**</v>
+        <v>**Bag leaks after vacuum sealing**</v>
       </c>
       <c r="F184" t="str">
         <v>review</v>
@@ -4648,7 +4648,7 @@
         <v>高温胶布破损或脱落</v>
       </c>
       <c r="E185" t="str">
-        <v>高温胶布破损或脱落</v>
+        <v>Heat-resistant tape is damaged or detached</v>
       </c>
       <c r="F185" t="str">
         <v>review</v>
@@ -4671,7 +4671,7 @@
         <v>及时替换高温胶布。</v>
       </c>
       <c r="E186" t="str">
-        <v>及时替换高温胶布。</v>
+        <v>Replace the heat-resistant tape promptly.</v>
       </c>
       <c r="F186" t="str">
         <v>review</v>
@@ -4694,7 +4694,7 @@
         <v>发热温度异常导致袋子融化或密封不充分</v>
       </c>
       <c r="E187" t="str">
-        <v>发热温度异常导致袋子融化或密封不充分</v>
+        <v>Abnormal heating melts the bag or weakens the seal</v>
       </c>
       <c r="F187" t="str">
         <v>review</v>
@@ -4717,7 +4717,7 @@
         <v>参考抽气不干净和不能密封的解决方案。</v>
       </c>
       <c r="E188" t="str">
-        <v>参考抽气不干净和不能密封的解决方案。</v>
+        <v>Refer to the solutions for weak vacuum or sealing failure.</v>
       </c>
       <c r="F188" t="str">
         <v>review</v>
@@ -4740,7 +4740,7 @@
         <v>锋利物品刺穿袋子</v>
       </c>
       <c r="E189" t="str">
-        <v>锋利物品刺穿袋子</v>
+        <v>Sharp items puncture the bag</v>
       </c>
       <c r="F189" t="str">
         <v>review</v>
@@ -4763,7 +4763,7 @@
         <v>用纸巾或防刺穿片包裹锋利边缘，使用新袋重试。</v>
       </c>
       <c r="E190" t="str">
-        <v>用纸巾或防刺穿片包裹锋利边缘，使用新袋重试。</v>
+        <v>Wrap sharp edges with paper towel or a puncture guard and retry with a new bag.</v>
       </c>
       <c r="F190" t="str">
         <v>review</v>
@@ -5177,7 +5177,7 @@
         <v>一些水果和蔬菜在包装前如果没有正确地焯熟，或者热的食物，会释放气体，导致真空袋没有收紧，此类情况属于正常表现，不属于漏气。</v>
       </c>
       <c r="E208" t="str">
-        <v>一些水果和蔬菜在包装前如果没有正确地焯熟，或者热的食物，会释放气体，导致真空袋没有收紧，此类情况属于正常表现，不属于漏气。</v>
+        <v>Some fruits and vegetables may release gas if they are not blanched properly before packing. Hot food may also release gas. If the bag does not stay tight in these cases, it is normal and does not indicate a leak.</v>
       </c>
       <c r="F208" t="str">
         <v>review</v>
@@ -5200,7 +5200,7 @@
         <v>提示</v>
       </c>
       <c r="E209" t="str">
-        <v>提示</v>
+        <v>Notice</v>
       </c>
       <c r="F209" t="str">
         <v>review</v>
@@ -5223,7 +5223,7 @@
         <v>若以上故障排除方案均无法解决问题，请联系客服指引解决，请不要擅自拆卸机器。</v>
       </c>
       <c r="E210" t="str">
-        <v>若以上故障排除方案均无法解决问题，请联系客服指引解决，请不要擅自拆卸机器。</v>
+        <v>If the issue remains after the steps above, contact customer service for guidance. Do not disassemble the machine yourself.</v>
       </c>
       <c r="F210" t="str">
         <v>review</v>
@@ -5499,7 +5499,7 @@
         <v>**错误报警（蜂鸣声长鸣 + 指示灯快闪）**</v>
       </c>
       <c r="E222" t="str">
-        <v>**错误报警（蜂鸣声长鸣 + 指示灯快闪）**</v>
+        <v>**Error alarm (long buzzer + fast flashing indicator)**</v>
       </c>
       <c r="F222" t="str">
         <v>review</v>
@@ -5522,7 +5522,7 @@
         <v>按下 Vac&amp;Seal/Start 或 Seal 后报警</v>
       </c>
       <c r="E223" t="str">
-        <v>按下 Vac&amp;Seal/Start 或 Seal 后报警</v>
+        <v>Alarm sounds after pressing Vac&amp;Seal/Start or Seal</v>
       </c>
       <c r="F223" t="str">
         <v>review</v>
@@ -5545,7 +5545,7 @@
         <v>检查面盖是否闭合，把手是否已下压锁紧。</v>
       </c>
       <c r="E224" t="str">
-        <v>检查面盖是否闭合，把手是否已下压锁紧。</v>
+        <v>Check whether the lid is closed and the handle is pressed down and locked.</v>
       </c>
       <c r="F224" t="str">
         <v>review</v>
@@ -5568,7 +5568,7 @@
         <v>真空工作过程中连续蜂鸣</v>
       </c>
       <c r="E225" t="str">
-        <v>真空工作过程中连续蜂鸣</v>
+        <v>Continuous beeping during vacuuming</v>
       </c>
       <c r="F225" t="str">
         <v>review</v>
@@ -5591,7 +5591,7 @@
         <v>机器无法达到目标压力，检查把手锁紧及袋子是否破损，更换新袋重试。</v>
       </c>
       <c r="E226" t="str">
-        <v>机器无法达到目标压力，检查把手锁紧及袋子是否破损，更换新袋重试。</v>
+        <v>The machine cannot reach the target pressure. Check that the handle is locked and the bag is not damaged. Retry with a new bag.</v>
       </c>
       <c r="F226" t="str">
         <v>review</v>
@@ -5637,7 +5637,7 @@
         <v>如因特殊原因，导致液体进入机器内部的处理方案</v>
       </c>
       <c r="E228" t="str">
-        <v>如因特殊原因，导致液体进入机器内部的处理方案</v>
+        <v>Handling procedure if liquid enters the machine for any special reason</v>
       </c>
       <c r="F228" t="str">
         <v>review</v>
@@ -5660,7 +5660,7 @@
         <v>**液体进入真空腔中：**</v>
       </c>
       <c r="E229" t="str">
-        <v>**液体进入真空腔中：**</v>
+        <v>**Liquid enters the vacuum chamber:**</v>
       </c>
       <c r="F229" t="str">
         <v>review</v>
@@ -5683,7 +5683,7 @@
         <v>立即关闭电源，等待至少 5 分钟，让机器发热器冷却。</v>
       </c>
       <c r="E230" t="str">
-        <v>立即关闭电源，等待至少 5 分钟，让机器发热器冷却。</v>
+        <v>Turn off the power immediately and wait at least 5 minutes for the heater to cool down.</v>
       </c>
       <c r="F230" t="str">
         <v>review</v>
@@ -5706,7 +5706,7 @@
         <v>将液体槽取出，并清理擦干液体。</v>
       </c>
       <c r="E231" t="str">
-        <v>将液体槽取出，并清理擦干液体。</v>
+        <v>Remove the liquid tray and wipe away the liquid.</v>
       </c>
       <c r="F231" t="str">
         <v>review</v>
@@ -5729,7 +5729,7 @@
         <v>将真空腔中的液体擦干。</v>
       </c>
       <c r="E232" t="str">
-        <v>将真空腔中的液体擦干。</v>
+        <v>Wipe the liquid out of the vacuum chamber.</v>
       </c>
       <c r="F232" t="str">
         <v>review</v>
@@ -5752,7 +5752,7 @@
         <v>将机器底部铺垫厨房纸或托盘，重新通电。</v>
       </c>
       <c r="E233" t="str">
-        <v>将机器底部铺垫厨房纸或托盘，重新通电。</v>
+        <v>Place kitchen paper or a tray under the machine, then power it on again.</v>
       </c>
       <c r="F233" t="str">
         <v>review</v>
@@ -5775,7 +5775,7 @@
         <v>合上面盖，长按 [btn:Pulse Vac] 按键抽气 20 秒，然后点击 [btn:Stop] 排气，重复 5 次，让内部管道的液体排出。</v>
       </c>
       <c r="E234" t="str">
-        <v>合上面盖，长按 [btn:Pulse Vac] 按键抽气 20 秒，然后点击 [btn:Stop] 排气，重复 5 次，让内部管道的液体排出。</v>
+        <v>Close the lid, hold [btn:Pulse Vac] for 20 seconds, then tap [btn:Stop] to vent. Repeat 5 times to expel liquid from the internal tube.</v>
       </c>
       <c r="F234" t="str">
         <v>review</v>
@@ -5798,7 +5798,7 @@
         <v>打开面盖，在机器底部铺垫厨房纸或托盘，将机器放置于通风处晾干 48 小时，期间不要翻倒机器。</v>
       </c>
       <c r="E235" t="str">
-        <v>打开面盖，在机器底部铺垫厨房纸或托盘，将机器放置于通风处晾干 48 小时，期间不要翻倒机器。</v>
+        <v>Open the lid, place kitchen paper or a tray under the machine, and leave it in a ventilated place to dry for 48 hours. Do not tilt or invert the machine.</v>
       </c>
       <c r="F235" t="str">
         <v>review</v>
@@ -5821,7 +5821,7 @@
         <v>**液体进入发热器：**</v>
       </c>
       <c r="E236" t="str">
-        <v>**液体进入发热器：**</v>
+        <v>**Liquid enters the heater:**</v>
       </c>
       <c r="F236" t="str">
         <v>review</v>
@@ -5844,7 +5844,7 @@
         <v>请勿翻倒机器，关闭电源，等待 10 分钟，让发热器冷却及内部液体排出。</v>
       </c>
       <c r="E237" t="str">
-        <v>请勿翻倒机器，关闭电源，等待 10 分钟，让发热器冷却及内部液体排出。</v>
+        <v>Do not invert the machine. Turn off the power and wait 10 minutes for the heater to cool and the internal liquid to drain.</v>
       </c>
       <c r="F237" t="str">
         <v>review</v>
@@ -5867,7 +5867,7 @@
         <v>清理和擦干机器接水盘、真空腔、底部的液体。</v>
       </c>
       <c r="E238" t="str">
-        <v>清理和擦干机器接水盘、真空腔、底部的液体。</v>
+        <v>Clean and dry the drip tray, vacuum chamber, and the liquid at the bottom.</v>
       </c>
       <c r="F238" t="str">
         <v>review</v>
@@ -5890,7 +5890,7 @@
         <v>打开面盖，在机器底部铺垫厨房纸或托盘，将机器放置于通风处晾干 24 小时，期间不要翻倒机器。</v>
       </c>
       <c r="E239" t="str">
-        <v>打开面盖，在机器底部铺垫厨房纸或托盘，将机器放置于通风处晾干 24 小时，期间不要翻倒机器。</v>
+        <v>Open the lid, place kitchen paper or a tray under the machine, and leave it in a ventilated place to dry for 24 hours. Do not tilt or invert the machine.</v>
       </c>
       <c r="F239" t="str">
         <v>review</v>
@@ -5913,7 +5913,7 @@
         <v>将机器底部铺垫厨房纸或托盘，重新通电。</v>
       </c>
       <c r="E240" t="str">
-        <v>将机器底部铺垫厨房纸或托盘，重新通电。</v>
+        <v>Place kitchen paper or a tray under the machine, then power it on again.</v>
       </c>
       <c r="F240" t="str">
         <v>review</v>
@@ -5936,7 +5936,7 @@
         <v>合上面盖，长按 [btn:Pulse Vac] 按键抽气 20 秒，然后点击 [btn:Stop] 排气，重复 5 次，让内部管道的液体排出。</v>
       </c>
       <c r="E241" t="str">
-        <v>合上面盖，长按 [btn:Pulse Vac] 按键抽气 20 秒，然后点击 [btn:Stop] 排气，重复 5 次，让内部管道的液体排出。</v>
+        <v>Close the lid, hold [btn:Pulse Vac] for 20 seconds, then tap [btn:Stop] to vent. Repeat 5 times to expel liquid from the internal tube.</v>
       </c>
       <c r="F241" t="str">
         <v>review</v>
@@ -5959,7 +5959,7 @@
         <v>打开面盖，在机器底部铺垫厨房纸或托盘，将机器放置于通风处晾干 48 小时，期间不要翻倒机器。</v>
       </c>
       <c r="E242" t="str">
-        <v>打开面盖，在机器底部铺垫厨房纸或托盘，将机器放置于通风处晾干 48 小时，期间不要翻倒机器。</v>
+        <v>Open the lid, place kitchen paper or a tray under the machine, and leave it in a ventilated place to dry for 48 hours. Do not tilt or invert the machine.</v>
       </c>
       <c r="F242" t="str">
         <v>review</v>
@@ -5982,7 +5982,7 @@
         <v>如果长期不清洁，内部管道可能会堵塞，影响抽气性能，此时请联系售后进行管道更换。</v>
       </c>
       <c r="E243" t="str">
-        <v>如果长期不清洁，内部管道可能会堵塞，影响抽气性能，此时请联系售后进行管道更换。</v>
+        <v>If the internal tubing is not cleaned for a long time, it may clog and reduce vacuum performance. Contact after-sales service for tube replacement.</v>
       </c>
       <c r="F243" t="str">
         <v>review</v>
@@ -6005,7 +6005,7 @@
         <v>注意</v>
       </c>
       <c r="E244" t="str">
-        <v>注意</v>
+        <v>Caution</v>
       </c>
       <c r="F244" t="str">
         <v>review</v>
